--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -3374,7 +3374,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>

--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -13861,20 +13861,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>468.8927935526</v>
-      </c>
-      <c r="C3" s="3">
-        <v>660.0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>132.0790560447</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>

--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -4939,9 +4939,7 @@
       <c r="F3" s="3">
         <v>51.9993775139</v>
       </c>
-      <c r="G3" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3">
         <v>40.0</v>
       </c>
@@ -4978,9 +4976,7 @@
       <c r="F4" s="3">
         <v>110.4754655171</v>
       </c>
-      <c r="G4" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3">
         <v>40.0</v>
       </c>
@@ -5017,9 +5013,7 @@
       <c r="F5" s="3">
         <v>140.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3">
         <v>40.0</v>
       </c>
@@ -5056,9 +5050,7 @@
       <c r="F6" s="3">
         <v>140.0</v>
       </c>
-      <c r="G6" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
         <v>40.0</v>
       </c>
@@ -5095,9 +5087,7 @@
       <c r="F7" s="3">
         <v>140.0</v>
       </c>
-      <c r="G7" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>40.0</v>
       </c>
@@ -5134,9 +5124,7 @@
       <c r="F8" s="3">
         <v>140.0</v>
       </c>
-      <c r="G8" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3">
         <v>40.0</v>
       </c>
@@ -5173,9 +5161,7 @@
       <c r="F9" s="3">
         <v>140.0</v>
       </c>
-      <c r="G9" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3">
         <v>40.0</v>
       </c>
@@ -5212,9 +5198,7 @@
       <c r="F10" s="3">
         <v>140.0</v>
       </c>
-      <c r="G10" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3">
         <v>40.0</v>
       </c>
@@ -5251,9 +5235,7 @@
       <c r="F11" s="3">
         <v>140.0</v>
       </c>
-      <c r="G11" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3">
         <v>40.0</v>
       </c>
@@ -5290,9 +5272,7 @@
       <c r="F12" s="3">
         <v>158.3344152734</v>
       </c>
-      <c r="G12" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>40.0</v>
       </c>
@@ -5329,9 +5309,7 @@
       <c r="F13" s="3">
         <v>178.322823806</v>
       </c>
-      <c r="G13" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
         <v>40.0</v>
       </c>
@@ -5368,9 +5346,7 @@
       <c r="F14" s="3">
         <v>198.3112323386</v>
       </c>
-      <c r="G14" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3">
         <v>40.0</v>
       </c>
@@ -5407,9 +5383,7 @@
       <c r="F15" s="3">
         <v>218.2996408711</v>
       </c>
-      <c r="G15" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>40.0</v>
       </c>
@@ -5446,9 +5420,7 @@
       <c r="F16" s="3">
         <v>238.2880494037</v>
       </c>
-      <c r="G16" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
         <v>40.0</v>
       </c>
@@ -5485,9 +5457,7 @@
       <c r="F17" s="3">
         <v>258.2764579362</v>
       </c>
-      <c r="G17" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3">
         <v>40.0</v>
       </c>
@@ -5524,9 +5494,7 @@
       <c r="F18" s="3">
         <v>278.2648664688</v>
       </c>
-      <c r="G18" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
         <v>40.0</v>
       </c>
@@ -5563,9 +5531,7 @@
       <c r="F19" s="3">
         <v>298.2532750014</v>
       </c>
-      <c r="G19" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3">
         <v>40.0</v>
       </c>
@@ -5602,9 +5568,7 @@
       <c r="F20" s="3">
         <v>318.2416835339</v>
       </c>
-      <c r="G20" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3">
         <v>40.0</v>
       </c>
@@ -5641,9 +5605,7 @@
       <c r="F21" s="3">
         <v>338.2300920665</v>
       </c>
-      <c r="G21" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3">
         <v>40.0</v>
       </c>
@@ -5680,9 +5642,7 @@
       <c r="F22" s="3">
         <v>358.2185005991</v>
       </c>
-      <c r="G22" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3">
         <v>40.0</v>
       </c>
@@ -5719,9 +5679,7 @@
       <c r="F23" s="3">
         <v>378.2069091316</v>
       </c>
-      <c r="G23" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3">
         <v>40.0</v>
       </c>
@@ -5758,9 +5716,7 @@
       <c r="F24" s="3">
         <v>398.1953176642</v>
       </c>
-      <c r="G24" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3">
         <v>40.0</v>
       </c>
@@ -5797,9 +5753,7 @@
       <c r="F25" s="3">
         <v>400.0</v>
       </c>
-      <c r="G25" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3">
         <v>40.0</v>
       </c>
@@ -5836,9 +5790,7 @@
       <c r="F26" s="3">
         <v>400.0</v>
       </c>
-      <c r="G26" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3">
         <v>40.0</v>
       </c>
@@ -5875,9 +5827,7 @@
       <c r="F27" s="3">
         <v>400.0</v>
       </c>
-      <c r="G27" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3">
         <v>40.0</v>
       </c>
@@ -5914,9 +5864,7 @@
       <c r="F28" s="3">
         <v>400.0</v>
       </c>
-      <c r="G28" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3">
         <v>40.0</v>
       </c>
@@ -5953,9 +5901,7 @@
       <c r="F29" s="3">
         <v>400.0</v>
       </c>
-      <c r="G29" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3">
         <v>40.0</v>
       </c>
@@ -5992,9 +5938,7 @@
       <c r="F30" s="3">
         <v>400.0</v>
       </c>
-      <c r="G30" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3">
         <v>40.0</v>
       </c>
@@ -6031,9 +5975,7 @@
       <c r="F31" s="3">
         <v>400.0</v>
       </c>
-      <c r="G31" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="3">
         <v>40.0</v>
       </c>
@@ -6070,9 +6012,7 @@
       <c r="F32" s="3">
         <v>400.0</v>
       </c>
-      <c r="G32" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="3">
         <v>40.0</v>
       </c>
@@ -6109,9 +6049,7 @@
       <c r="F33" s="3">
         <v>400.0</v>
       </c>
-      <c r="G33" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="3">
         <v>40.0</v>
       </c>
@@ -6148,9 +6086,7 @@
       <c r="F34" s="3">
         <v>400.0</v>
       </c>
-      <c r="G34" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="3">
         <v>40.0</v>
       </c>
@@ -6187,9 +6123,7 @@
       <c r="F35" s="3">
         <v>400.0</v>
       </c>
-      <c r="G35" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3">
         <v>40.0</v>
       </c>
@@ -6226,9 +6160,7 @@
       <c r="F36" s="3">
         <v>400.0</v>
       </c>
-      <c r="G36" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="3">
         <v>40.0</v>
       </c>
@@ -6265,9 +6197,7 @@
       <c r="F37" s="3">
         <v>400.0</v>
       </c>
-      <c r="G37" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3">
         <v>40.0</v>
       </c>
@@ -6304,9 +6234,7 @@
       <c r="F38" s="3">
         <v>400.0</v>
       </c>
-      <c r="G38" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="3">
         <v>40.0</v>
       </c>
@@ -6343,9 +6271,7 @@
       <c r="F39" s="3">
         <v>400.0</v>
       </c>
-      <c r="G39" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="3">
         <v>40.0</v>
       </c>
@@ -6382,9 +6308,7 @@
       <c r="F40" s="3">
         <v>400.0</v>
       </c>
-      <c r="G40" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="3">
         <v>40.0</v>
       </c>
@@ -6421,9 +6345,7 @@
       <c r="F41" s="3">
         <v>400.0</v>
       </c>
-      <c r="G41" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3">
         <v>40.0</v>
       </c>

--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -4939,7 +4939,9 @@
       <c r="F3" s="3">
         <v>51.9993775139</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H3" s="3">
         <v>40.0</v>
       </c>
@@ -4976,7 +4978,9 @@
       <c r="F4" s="3">
         <v>110.4754655171</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H4" s="3">
         <v>40.0</v>
       </c>
@@ -5013,7 +5017,9 @@
       <c r="F5" s="3">
         <v>140.0</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H5" s="3">
         <v>40.0</v>
       </c>
@@ -5050,7 +5056,9 @@
       <c r="F6" s="3">
         <v>140.0</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H6" s="3">
         <v>40.0</v>
       </c>
@@ -5087,7 +5095,9 @@
       <c r="F7" s="3">
         <v>140.0</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H7" s="3">
         <v>40.0</v>
       </c>
@@ -5124,7 +5134,9 @@
       <c r="F8" s="3">
         <v>140.0</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H8" s="3">
         <v>40.0</v>
       </c>
@@ -5161,7 +5173,9 @@
       <c r="F9" s="3">
         <v>140.0</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H9" s="3">
         <v>40.0</v>
       </c>
@@ -5198,7 +5212,9 @@
       <c r="F10" s="3">
         <v>140.0</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H10" s="3">
         <v>40.0</v>
       </c>
@@ -5235,7 +5251,9 @@
       <c r="F11" s="3">
         <v>140.0</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H11" s="3">
         <v>40.0</v>
       </c>
@@ -5272,7 +5290,9 @@
       <c r="F12" s="3">
         <v>158.3344152734</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H12" s="3">
         <v>40.0</v>
       </c>
@@ -5309,7 +5329,9 @@
       <c r="F13" s="3">
         <v>178.322823806</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H13" s="3">
         <v>40.0</v>
       </c>
@@ -5346,7 +5368,9 @@
       <c r="F14" s="3">
         <v>198.3112323386</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H14" s="3">
         <v>40.0</v>
       </c>
@@ -5383,7 +5407,9 @@
       <c r="F15" s="3">
         <v>218.2996408711</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H15" s="3">
         <v>40.0</v>
       </c>
@@ -5420,7 +5446,9 @@
       <c r="F16" s="3">
         <v>238.2880494037</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H16" s="3">
         <v>40.0</v>
       </c>
@@ -5457,7 +5485,9 @@
       <c r="F17" s="3">
         <v>258.2764579362</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H17" s="3">
         <v>40.0</v>
       </c>
@@ -5494,7 +5524,9 @@
       <c r="F18" s="3">
         <v>278.2648664688</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H18" s="3">
         <v>40.0</v>
       </c>
@@ -5531,7 +5563,9 @@
       <c r="F19" s="3">
         <v>298.2532750014</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H19" s="3">
         <v>40.0</v>
       </c>
@@ -5568,7 +5602,9 @@
       <c r="F20" s="3">
         <v>318.2416835339</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H20" s="3">
         <v>40.0</v>
       </c>
@@ -5605,7 +5641,9 @@
       <c r="F21" s="3">
         <v>338.2300920665</v>
       </c>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H21" s="3">
         <v>40.0</v>
       </c>
@@ -5642,7 +5680,9 @@
       <c r="F22" s="3">
         <v>358.2185005991</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H22" s="3">
         <v>40.0</v>
       </c>
@@ -5679,7 +5719,9 @@
       <c r="F23" s="3">
         <v>378.2069091316</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H23" s="3">
         <v>40.0</v>
       </c>
@@ -5716,7 +5758,9 @@
       <c r="F24" s="3">
         <v>398.1953176642</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H24" s="3">
         <v>40.0</v>
       </c>
@@ -5753,7 +5797,9 @@
       <c r="F25" s="3">
         <v>400.0</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H25" s="3">
         <v>40.0</v>
       </c>
@@ -5790,7 +5836,9 @@
       <c r="F26" s="3">
         <v>400.0</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H26" s="3">
         <v>40.0</v>
       </c>
@@ -5827,7 +5875,9 @@
       <c r="F27" s="3">
         <v>400.0</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H27" s="3">
         <v>40.0</v>
       </c>
@@ -5864,7 +5914,9 @@
       <c r="F28" s="3">
         <v>400.0</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H28" s="3">
         <v>40.0</v>
       </c>
@@ -5901,7 +5953,9 @@
       <c r="F29" s="3">
         <v>400.0</v>
       </c>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H29" s="3">
         <v>40.0</v>
       </c>
@@ -5938,7 +5992,9 @@
       <c r="F30" s="3">
         <v>400.0</v>
       </c>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H30" s="3">
         <v>40.0</v>
       </c>
@@ -5975,7 +6031,9 @@
       <c r="F31" s="3">
         <v>400.0</v>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H31" s="3">
         <v>40.0</v>
       </c>
@@ -6012,7 +6070,9 @@
       <c r="F32" s="3">
         <v>400.0</v>
       </c>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H32" s="3">
         <v>40.0</v>
       </c>
@@ -6049,7 +6109,9 @@
       <c r="F33" s="3">
         <v>400.0</v>
       </c>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H33" s="3">
         <v>40.0</v>
       </c>
@@ -6086,7 +6148,9 @@
       <c r="F34" s="3">
         <v>400.0</v>
       </c>
-      <c r="G34" s="3"/>
+      <c r="G34" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H34" s="3">
         <v>40.0</v>
       </c>
@@ -6123,7 +6187,9 @@
       <c r="F35" s="3">
         <v>400.0</v>
       </c>
-      <c r="G35" s="3"/>
+      <c r="G35" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H35" s="3">
         <v>40.0</v>
       </c>
@@ -6160,7 +6226,9 @@
       <c r="F36" s="3">
         <v>400.0</v>
       </c>
-      <c r="G36" s="3"/>
+      <c r="G36" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H36" s="3">
         <v>40.0</v>
       </c>
@@ -6197,7 +6265,9 @@
       <c r="F37" s="3">
         <v>400.0</v>
       </c>
-      <c r="G37" s="3"/>
+      <c r="G37" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H37" s="3">
         <v>40.0</v>
       </c>
@@ -6234,7 +6304,9 @@
       <c r="F38" s="3">
         <v>400.0</v>
       </c>
-      <c r="G38" s="3"/>
+      <c r="G38" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H38" s="3">
         <v>40.0</v>
       </c>
@@ -6271,7 +6343,9 @@
       <c r="F39" s="3">
         <v>400.0</v>
       </c>
-      <c r="G39" s="3"/>
+      <c r="G39" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H39" s="3">
         <v>40.0</v>
       </c>
@@ -6308,7 +6382,9 @@
       <c r="F40" s="3">
         <v>400.0</v>
       </c>
-      <c r="G40" s="3"/>
+      <c r="G40" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H40" s="3">
         <v>40.0</v>
       </c>
@@ -6345,7 +6421,9 @@
       <c r="F41" s="3">
         <v>400.0</v>
       </c>
-      <c r="G41" s="3"/>
+      <c r="G41" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H41" s="3">
         <v>40.0</v>
       </c>
